--- a/entorno/mir-v2/archivos_de_prueba/Chubut_correctos/LEGAJO_NYA_2026_T1_Chubut.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chubut_correctos/LEGAJO_NYA_2026_T1_Chubut.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="NyA" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Prov_Dto_Localidad" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="INSTRUCCIONES" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="LISTAS" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NyA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prov_Dto_Localidad" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/entorno/mir-v2/archivos_de_prueba/Chubut_correctos/LEGAJO_NYA_2026_T1_Chubut.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chubut_correctos/LEGAJO_NYA_2026_T1_Chubut.xlsx
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="U3" s="4" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="4">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="U4" s="4" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
     </row>
     <row r="5">
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="U5" s="4" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
     </row>
     <row r="6">
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="U6" s="4" t="n">
-        <v>45609</v>
+        <v>45610</v>
       </c>
     </row>
     <row r="7">
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="U7" s="4" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
     </row>
     <row r="8">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="U8" s="4" t="n">
-        <v>45954</v>
+        <v>45955</v>
       </c>
     </row>
     <row r="9">
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="U9" s="4" t="n">
-        <v>45628</v>
+        <v>45629</v>
       </c>
     </row>
     <row r="10">
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="U10" s="4" t="n">
-        <v>45781</v>
+        <v>45782</v>
       </c>
     </row>
     <row r="11">
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="U11" s="4" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="12">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="U12" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="13">
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="U13" s="4" t="n">
-        <v>45734</v>
+        <v>45735</v>
       </c>
     </row>
     <row r="14">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="U14" s="4" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
     </row>
     <row r="15">
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="U15" s="4" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="16">
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="U16" s="4" t="n">
-        <v>45684</v>
+        <v>45685</v>
       </c>
     </row>
     <row r="17">
@@ -2308,7 +2308,7 @@
         </is>
       </c>
       <c r="U17" s="4" t="n">
-        <v>45601</v>
+        <v>45602</v>
       </c>
     </row>
     <row r="18">
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="U18" s="4" t="n">
-        <v>45845</v>
+        <v>45846</v>
       </c>
     </row>
     <row r="19">
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>45827</v>
+        <v>45828</v>
       </c>
     </row>
     <row r="20">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="U20" s="4" t="n">
-        <v>45870</v>
+        <v>45871</v>
       </c>
     </row>
     <row r="21">
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="U21" s="4" t="n">
-        <v>45788</v>
+        <v>45789</v>
       </c>
     </row>
     <row r="22">
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="U22" s="4" t="n">
-        <v>45743</v>
+        <v>45744</v>
       </c>
     </row>
     <row r="23">
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="U23" s="4" t="n">
-        <v>45652</v>
+        <v>45653</v>
       </c>
     </row>
     <row r="24">
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="U24" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
     </row>
     <row r="25">
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="U25" s="4" t="n">
-        <v>45838</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="26">
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="U26" s="4" t="n">
-        <v>45720</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="27">
@@ -3298,7 +3298,7 @@
         </is>
       </c>
       <c r="U27" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="28">
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="U28" s="4" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="29">
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="U29" s="4" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
     </row>
     <row r="30">
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="U30" s="4" t="n">
-        <v>45601</v>
+        <v>45602</v>
       </c>
     </row>
     <row r="31">
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="U31" s="4" t="n">
-        <v>46053</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="32">
@@ -3787,7 +3787,7 @@
         </is>
       </c>
       <c r="U32" s="4" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="33">

--- a/entorno/mir-v2/archivos_de_prueba/Chubut_correctos/LEGAJO_NYA_2026_T1_Chubut.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chubut_correctos/LEGAJO_NYA_2026_T1_Chubut.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NyA" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prov_Dto_Localidad" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="NyA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Prov_Dto_Localidad" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Listas" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,10 +35,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="5">
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -102,10 +97,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -185,182 +176,171 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>RUNAC</author>
+    <author>MIR</author>
   </authors>
   <commentList>
     <comment ref="A2" authorId="0" shapeId="0">
       <text>
-        <t>ID del Niño, niña o Adolescente
-Identificador que le asigna el sistema provincial al niño, niña o adolescente. Es la clave con la que las nóminas (MPE, MPI, MPJ) se enganchan a este legajo.
-Qué se espera: un número entero
-Campo obligatorio.</t>
+        <t>ID del niño, niña o adolescente
+Obligatorio
+Qué va: Número entero.
+Identificador que le asigna el sistema provincial al niño, niña o adolescente. Es la clave con la que las nóminas (MPE, MPI, MPJ) se enganchan a este legajo.</t>
       </text>
     </comment>
     <comment ref="B2" authorId="0" shapeId="0">
       <text>
         <t>Apellido/s
-Qué se espera: texto
-Máximo 120 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="C2" authorId="0" shapeId="0">
       <text>
         <t>Nombre/s
-Qué se espera: texto
-Máximo 120 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="D2" authorId="0" shapeId="0">
       <text>
         <t>Tipo de documento de identidad
-Qué se espera: texto
-Máximo 26 caracteres.
-Elegir de la lista "Tipo de documento de identidad".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: DNI, Documento extranjero, Otro tipo de documentación, Sin documentación.</t>
       </text>
     </comment>
     <comment ref="E2" authorId="0" shapeId="0">
       <text>
         <t>Nº DNI
-Qué se espera: texto
-Máximo 15 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 15 caracteres.
+No se puede repetir en la hoja.</t>
       </text>
     </comment>
     <comment ref="F2" authorId="0" shapeId="0">
       <text>
         <t>Nº de CUIL
-Qué se espera: texto
-Máximo 13 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 13 caracteres.
+Tiene que ser un CUIL válido: se controla el dígito verificador.
+Aviso: Con el formato NN-NNNNNNNN-N.</t>
       </text>
     </comment>
     <comment ref="G2" authorId="0" shapeId="0">
       <text>
         <t>Otro núero de documentación de identidad (si no cuenta con DNI)
-Qué se espera: texto
-Máximo 15 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 15 caracteres.
+No se puede repetir en la hoja.</t>
       </text>
     </comment>
     <comment ref="H2" authorId="0" shapeId="0">
       <text>
         <t>Género
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Género".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Masculino, Femenino, Otros.</t>
       </text>
     </comment>
     <comment ref="I2" authorId="0" shapeId="0">
       <text>
         <t>País de nacimiento
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "País de nacimiento (legajo)".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: 11 opciones, en el desplegable.</t>
       </text>
     </comment>
     <comment ref="J2" authorId="0" shapeId="0">
       <text>
         <t>Fecha de nacimiento
-Qué se espera: una fecha, con formato dd/mm/aaaa
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Fecha, como día/mes/año.
+Aviso: No puede ser posterior a hoy.</t>
       </text>
     </comment>
     <comment ref="K2" authorId="0" shapeId="0">
       <text>
         <t>Domicilio actual
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="L2" authorId="0" shapeId="0">
       <text>
         <t>Provincia
-Qué se espera: texto
-Máximo 120 caracteres.
-Elegir de la lista "Provincia (nomenclador oficial)".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.</t>
       </text>
     </comment>
     <comment ref="M2" authorId="0" shapeId="0">
       <text>
         <t>Departamento
-Qué se espera: texto
-Elegir de la lista "Departamento (nomenclador oficial)".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Aviso: No puede ser posterior a hoy.</t>
       </text>
     </comment>
     <comment ref="N2" authorId="0" shapeId="0">
       <text>
         <t>Localidad
-Qué se espera: texto
-Máximo 120 caracteres.
-Elegir de la lista "Localidad (lista de la jurisdicción)".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.</t>
       </text>
     </comment>
     <comment ref="O2" authorId="0" shapeId="0">
       <text>
         <t>¿Pertenece a pueblo originario? (o se identifica con algún pueblo originario?)
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.</t>
       </text>
     </comment>
     <comment ref="P2" authorId="0" shapeId="0">
       <text>
         <t>Pueblo originario (especificar)
-Qué se espera: texto
-No es obligatorio.</t>
+Obligatorio según otro dato
+Qué va: Texto.
+Obligatorio si «¿Pertenece a pueblo originario? (o se identifica con algún pueblo originario?)» es «Sí».</t>
       </text>
     </comment>
     <comment ref="Q2" authorId="0" shapeId="0">
       <text>
         <t>¿Presenta algún tipo de discapacidad?
-Qué se espera: texto
-Máximo 24 caracteres.
-Elegir de la lista "Discapacidad (legajo)".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No presenta discapacidad, Visual, Auditiva, Mental, Motora, Visceral, Otros, Sin dato.</t>
       </text>
     </comment>
     <comment ref="R2" authorId="0" shapeId="0">
       <text>
         <t>¿Posee CUD?
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Posee CUD?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, En trámite, Vencido, No aplica, Sin datos.</t>
       </text>
     </comment>
     <comment ref="S2" authorId="0" shapeId="0">
       <text>
         <t>Cobertura salud
-Qué se espera: texto
-Máximo 22 caracteres.
-Elegir de la lista "Cobertura salud (legajo)".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Pública exclusivamente, Obra Social, Prepaga, Otra cobertura, Sin datos.</t>
       </text>
     </comment>
     <comment ref="T2" authorId="0" shapeId="0">
       <text>
         <t>¿Tiene hijos/as?
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.</t>
       </text>
     </comment>
     <comment ref="U2" authorId="0" shapeId="0">
       <text>
         <t>Fecha de actualización
-Qué se espera: una fecha, con formato dd/mm/aaaa
-No es obligatorio.</t>
+Opcional
+Qué va: Fecha, como día/mes/año.
+Aviso: No puede ser posterior a hoy.</t>
       </text>
     </comment>
   </commentList>
@@ -370,31 +350,28 @@
 <file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>RUNAC</author>
+    <author>MIR</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <t>PROVINCIA
-Qué se espera: texto
-Máximo 120 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <t>DEPTO
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
         <t>LOCALIDAD
-Qué se espera: texto
-Máximo 120 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
   </commentList>
@@ -720,7 +697,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ID del Niño, niña o Adolescente *</t>
+          <t>ID del niño, niña o adolescente *</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
@@ -845,7 +822,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>90000137</t>
+          <t>90000172</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -855,25 +832,25 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>90000137</t>
+          <t>90000168</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="J3" s="4" t="n">
-        <v>41182</v>
+        <v>40598</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Belgrano 1243</t>
+          <t>Alberdi 4567</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -888,41 +865,41 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Lago Puelo</t>
+          <t>Trelew</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Mapuche</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>No presenta discapacidad</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Obra Social</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 1</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Visual</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>No aplica</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>Otra cobertura</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="U3" s="4" t="n">
-        <v>46257</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="4">
@@ -931,12 +908,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fernández</t>
+          <t>Ledesma</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mateo</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -946,7 +923,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>90000274</t>
+          <t>90000357</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -956,7 +933,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>90000274</t>
+          <t>90000363</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -966,15 +943,15 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="J4" s="4" t="n">
-        <v>40287</v>
+        <v>41081</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Sarmiento 1728</t>
+          <t>Mitre 4927</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -989,19 +966,15 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Lago Puelo</t>
+          <t>Esquel</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 2</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
           <t>Otros</t>
@@ -1009,21 +982,21 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
+          <t>En trámite</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Prepaga</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Otra cobertura</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="U4" s="4" t="n">
-        <v>46003</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="5">
@@ -1037,7 +1010,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Thiago</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1047,7 +1020,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>90000411</t>
+          <t>90000422</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1057,7 +1030,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>90000411</t>
+          <t>90000459</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1067,15 +1040,15 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>41572</v>
+        <v>41587</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Rivadavia 1373</t>
+          <t>Sarmiento 2266</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1090,37 +1063,41 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Puerto Madryn</t>
+          <t>El Hoyo</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 3</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Sin dato</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Pública exclusivamente</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Visual</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>Vencido</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Pública exclusivamente</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="U5" s="4" t="n">
-        <v>45935</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="6">
@@ -1129,7 +1106,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ledesma</t>
+          <t>Quiroga</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1139,12 +1116,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>Otro tipo de documentación</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>90000548</t>
+          <t>90000621</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1154,7 +1131,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>90000548</t>
+          <t>90000572</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1164,15 +1141,15 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="J6" s="4" t="n">
-        <v>42375</v>
+        <v>40366</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>San Martín 3200</t>
+          <t>Alberdi 1966</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1187,41 +1164,37 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Trelew</t>
+          <t>El Hoyo</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Mental</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Qom</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Mental</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Otra cobertura</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>Pública exclusivamente</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="U6" s="4" t="n">
-        <v>45610</v>
+        <v>45827</v>
       </c>
     </row>
     <row r="7">
@@ -1230,12 +1203,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Martínez</t>
+          <t>Villalba</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Isabella</t>
+          <t>Lorenzo</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1245,7 +1218,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>90000685</t>
+          <t>90000705</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1255,12 +1228,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>90000685</t>
+          <t>90000732</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1269,11 +1242,11 @@
         </is>
       </c>
       <c r="J7" s="4" t="n">
-        <v>40592</v>
+        <v>41272</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Mitre 2377</t>
+          <t>Alberdi 684</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1288,7 +1261,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Dolavon</t>
+          <t>Trevelin</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1303,26 +1276,26 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Visceral</t>
+          <t>Auditiva</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>En trámite</t>
+          <t>Vencido</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Obra Social</t>
+          <t>Otra cobertura</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U7" s="4" t="n">
-        <v>46014</v>
+        <v>45636</v>
       </c>
     </row>
     <row r="8">
@@ -1336,17 +1309,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Martina</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>Documento extranjero</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>90000822</t>
+          <t>90000909</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1356,25 +1329,25 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>90000822</t>
+          <t>90000863</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v>40879</v>
+        <v>40310</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Sarmiento 2105</t>
+          <t>Güemes 2684</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1389,7 +1362,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Comodoro Rivadavia</t>
+          <t>Gaiman</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1400,17 +1373,17 @@
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Motora</t>
+          <t>Mental</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No aplica</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Prepaga</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1419,7 +1392,7 @@
         </is>
       </c>
       <c r="U8" s="4" t="n">
-        <v>45955</v>
+        <v>45620</v>
       </c>
     </row>
     <row r="9">
@@ -1428,22 +1401,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Paz</t>
+          <t>Díaz</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Isabella</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>Sin documentación</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>90000959</t>
+          <t>90000977</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1453,7 +1426,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>90000959</t>
+          <t>90000992</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1463,15 +1436,15 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>41471</v>
+        <v>42478</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Mitre 2293</t>
+          <t>Sarmiento 2252</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1486,41 +1459,41 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Trelew</t>
+          <t>Lago Puelo</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mapuche-Tehuelche</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Visceral</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 7</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Visceral</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Otra cobertura</t>
+          <t>Obra Social</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U9" s="4" t="n">
-        <v>45629</v>
+        <v>45786</v>
       </c>
     </row>
     <row r="10">
@@ -1529,22 +1502,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Díaz</t>
+          <t>Fernández</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sofía</t>
+          <t>Isabella</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Otro tipo de documentación</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>90001096</t>
+          <t>90001110</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1554,25 +1527,25 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>90001096</t>
+          <t>90001115</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="J10" s="4" t="n">
-        <v>42478</v>
+        <v>41908</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Sarmiento 2252</t>
+          <t>Sarmiento 620</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1587,41 +1560,41 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Lago Puelo</t>
+          <t>Gaiman</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 8</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Sin dato</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Prepaga</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Mapuche-Tehuelche</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Visceral</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>Obra Social</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="U10" s="4" t="n">
-        <v>45782</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="11">
@@ -1630,12 +1603,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fernández</t>
+          <t>Villalba</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Isabella</t>
+          <t>Bautista</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1645,7 +1618,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>90001233</t>
+          <t>90001320</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1655,25 +1628,25 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>90001233</t>
+          <t>90001301</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>40834</v>
+        <v>41572</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Güemes 3558</t>
+          <t>San Martín 2504</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1688,7 +1661,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Trevelin</t>
+          <t>Gaiman</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1699,17 +1672,17 @@
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>No presenta discapacidad</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>No aplica</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Otra cobertura</t>
+          <t>Prepaga</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1718,7 +1691,7 @@
         </is>
       </c>
       <c r="U11" s="4" t="n">
-        <v>46030</v>
+        <v>46109</v>
       </c>
     </row>
     <row r="12">
@@ -1732,7 +1705,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1742,7 +1715,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>90001370</t>
+          <t>90001450</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1752,7 +1725,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>90001370</t>
+          <t>90001408</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1762,15 +1735,15 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Perú</t>
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>42378</v>
+        <v>42673</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Güemes 2285</t>
+          <t>Belgrano 1352</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1785,32 +1758,32 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>El Hoyo</t>
+          <t>Sarmiento</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mapuche</t>
+          <t>Nota de ejemplo 10</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Motora</t>
+          <t>No presenta discapacidad</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Vencido</t>
+          <t>No aplica</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Obra Social</t>
+          <t>Prepaga</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1819,7 +1792,7 @@
         </is>
       </c>
       <c r="U12" s="4" t="n">
-        <v>46284</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="13">
@@ -1828,7 +1801,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Fernández</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1843,7 +1816,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>90001507</t>
+          <t>90001546</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1853,25 +1826,25 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>90001507</t>
+          <t>90001537</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>42258</v>
+        <v>42502</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>San Martín 2544</t>
+          <t>San Martín 801</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1886,41 +1859,37 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Lago Puelo</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Auditiva</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Otra cobertura</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 11</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Mental</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>Prepaga</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="U13" s="4" t="n">
-        <v>45735</v>
+        <v>46122</v>
       </c>
     </row>
     <row r="14">
@@ -1929,22 +1898,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ojeda</t>
+          <t>Rodríguez</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Martina</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>Sin documentación</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>90001644</t>
+          <t>90001671</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1954,7 +1923,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>90001644</t>
+          <t>90001713</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1964,15 +1933,15 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="J14" s="4" t="n">
-        <v>42180</v>
+        <v>41455</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>San Martín 1016</t>
+          <t>Mitre 3159</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1987,37 +1956,41 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Río Mayo</t>
+          <t>Dolavon</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mapuche</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Mental</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Pública exclusivamente</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Mental</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>Obra Social</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="U14" s="4" t="n">
-        <v>46207</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="15">
@@ -2026,22 +1999,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fernández</t>
+          <t>Ledesma</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bautista</t>
+          <t>Martina</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sin documentación</t>
+          <t>Documento extranjero</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>90001781</t>
+          <t>90001856</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2051,7 +2024,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>90001781</t>
+          <t>90001809</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2061,15 +2034,15 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Perú</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>40694</v>
+        <v>40420</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Belgrano 3993</t>
+          <t>Belgrano 652</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2084,7 +2057,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Rada Tilly</t>
+          <t>Río Mayo</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -2095,26 +2068,26 @@
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Visual</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No aplica</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
+          <t>Obra Social</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="U15" s="4" t="n">
-        <v>46082</v>
+        <v>45606</v>
       </c>
     </row>
     <row r="16">
@@ -2123,22 +2096,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Díaz</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Valentina</t>
+          <t>Mateo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sin documentación</t>
+          <t>Documento extranjero</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>90001918</t>
+          <t>90001991</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2148,25 +2121,25 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>90001918</t>
+          <t>90001991</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>41708</v>
+        <v>42116</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Mitre 4339</t>
+          <t>Güemes 3434</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2181,7 +2154,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Dolavon</t>
+          <t>Puerto Madryn</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2192,26 +2165,26 @@
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Mental</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>En trámite</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Prepaga</t>
+          <t>Otra cobertura</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U16" s="4" t="n">
-        <v>45685</v>
+        <v>45813</v>
       </c>
     </row>
     <row r="17">
@@ -2220,22 +2193,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Quiroga</t>
+          <t>Paz</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mateo</t>
+          <t>Bautista</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Documento extranjero</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>90002055</t>
+          <t>90002141</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2245,12 +2218,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>90002055</t>
+          <t>90002138</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2259,11 +2232,11 @@
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>40420</v>
+        <v>40427</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Belgrano 652</t>
+          <t>Mitre 2879</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2278,7 +2251,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Río Mayo</t>
+          <t>El Hoyo</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2289,17 +2262,17 @@
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Visual</t>
+          <t>Mental</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>No aplica</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>Obra Social</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -2308,7 +2281,7 @@
         </is>
       </c>
       <c r="U17" s="4" t="n">
-        <v>45602</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="18">
@@ -2317,22 +2290,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Díaz</t>
+          <t>Romero</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mateo</t>
+          <t>Sofía</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Documento extranjero</t>
+          <t>Otro tipo de documentación</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>90002192</t>
+          <t>90002251</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2342,25 +2315,25 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>90002192</t>
+          <t>90002223</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="J18" s="4" t="n">
-        <v>42539</v>
+        <v>42433</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Mitre 2090</t>
+          <t>San Martín 514</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2375,37 +2348,41 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>El Hoyo</t>
+          <t>El Maitén</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mapuche</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Mental</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Otra cobertura</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Mental</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Pública exclusivamente</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="U18" s="4" t="n">
-        <v>45846</v>
+        <v>45799</v>
       </c>
     </row>
     <row r="19">
@@ -2414,12 +2391,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sosa</t>
+          <t>Martínez</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Lorenzo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2429,7 +2406,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>90002329</t>
+          <t>90002336</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2439,7 +2416,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>90002329</t>
+          <t>90002350</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2453,11 +2430,11 @@
         </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v>40582</v>
+        <v>41778</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>San Martín 3398</t>
+          <t>Rivadavia 3827</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2472,7 +2449,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Lago Puelo</t>
+          <t>Esquel</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2480,10 +2457,14 @@
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 17</t>
+        </is>
+      </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Mental</t>
+          <t>Sin dato</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2498,11 +2479,11 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>45828</v>
+        <v>46069</v>
       </c>
     </row>
     <row r="20">
@@ -2511,22 +2492,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>López</t>
+          <t>Gómez</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Joaquín</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Documento extranjero</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>90002466</t>
+          <t>90002506</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2536,25 +2517,25 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>90002466</t>
+          <t>90002473</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="J20" s="4" t="n">
-        <v>41202</v>
+        <v>42131</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Güemes 717</t>
+          <t>Sarmiento 4450</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2569,41 +2550,41 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Dolavon</t>
+          <t>Comodoro Rivadavia</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 18</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Pública exclusivamente</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Mapuche</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>No presenta discapacidad</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Obra Social</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="U20" s="4" t="n">
-        <v>45871</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="21">
@@ -2612,12 +2593,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Díaz</t>
+          <t>Villalba</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Benjamín</t>
+          <t>Lorenzo</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2627,7 +2608,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>90002603</t>
+          <t>90002654</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2637,25 +2618,25 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>90002603</t>
+          <t>90002618</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>40853</v>
+        <v>42550</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Mitre 117</t>
+          <t>Sarmiento 425</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2670,28 +2651,28 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Gaiman</t>
+          <t>Trevelin</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Motora</t>
+          <t>Visceral</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Vencido</t>
+          <t>En trámite</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Obra Social</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -2700,7 +2681,7 @@
         </is>
       </c>
       <c r="U21" s="4" t="n">
-        <v>45789</v>
+        <v>45970</v>
       </c>
     </row>
     <row r="22">
@@ -2709,22 +2690,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>López</t>
+          <t>Martínez</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mateo</t>
+          <t>Valentina</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Otro tipo de documentación</t>
+          <t>Sin documentación</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>90002740</t>
+          <t>90002756</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2734,25 +2715,25 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>90002740</t>
+          <t>90002825</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="J22" s="4" t="n">
-        <v>42551</v>
+        <v>42051</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Alberdi 4541</t>
+          <t>Rivadavia 694</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2772,36 +2753,36 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 20</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Mapuche</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>No presenta discapacidad</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>No aplica</t>
-        </is>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Otra cobertura</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U22" s="4" t="n">
-        <v>45744</v>
+        <v>45773</v>
       </c>
     </row>
     <row r="23">
@@ -2810,22 +2791,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>López</t>
+          <t>Rodríguez</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Sofía</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>Otro tipo de documentación</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>90002877</t>
+          <t>90002885</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2835,25 +2816,25 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>90002877</t>
+          <t>90002908</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>42616</v>
+        <v>40825</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>San Martín 2026</t>
+          <t>Mitre 4550</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2868,12 +2849,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Gaiman</t>
+          <t>Lago Puelo</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2883,12 +2864,12 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Mental</t>
+          <t>No presenta discapacidad</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>No aplica</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2898,11 +2879,11 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U23" s="4" t="n">
-        <v>45653</v>
+        <v>45612</v>
       </c>
     </row>
     <row r="24">
@@ -2916,17 +2897,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Otro tipo de documentación</t>
+          <t>Documento extranjero</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>90003014</t>
+          <t>90003047</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2936,25 +2917,25 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>90003014</t>
+          <t>90003028</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Perú</t>
         </is>
       </c>
       <c r="J24" s="4" t="n">
-        <v>41465</v>
+        <v>40815</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Belgrano 2275</t>
+          <t>Rivadavia 2408</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2969,7 +2950,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Gaiman</t>
+          <t>Trevelin</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2984,12 +2965,12 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Motora</t>
+          <t>Visceral</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Vencido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2999,11 +2980,11 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U24" s="4" t="n">
-        <v>46278</v>
+        <v>45791</v>
       </c>
     </row>
     <row r="25">
@@ -3012,12 +2993,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Díaz</t>
+          <t>Rodríguez</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Joaquín</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3027,7 +3008,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>90003151</t>
+          <t>90003162</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3037,25 +3018,25 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>90003151</t>
+          <t>90003232</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Perú</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="J25" s="4" t="n">
-        <v>41052</v>
+        <v>40359</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Sarmiento 2272</t>
+          <t>San Martín 2832</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3070,37 +3051,41 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Comodoro Rivadavia</t>
+          <t>El Hoyo</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 23</t>
+        </is>
+      </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Mental</t>
+          <t>Motora</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>En trámite</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Prepaga</t>
+          <t>Otra cobertura</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U25" s="4" t="n">
-        <v>45839</v>
+        <v>45854</v>
       </c>
     </row>
     <row r="26">
@@ -3109,22 +3094,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Paz</t>
+          <t>Quiroga</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Martina</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Otro tipo de documentación</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>90003288</t>
+          <t>90003297</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3134,74 +3119,74 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>90003288</t>
+          <t>90003376</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>40326</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Güemes 3124</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Chubut</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Dato 24</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Trevelin</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Mapuche-Tehuelche</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Auditiva</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Prepaga</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="J26" s="4" t="n">
-        <v>42345</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>San Martín 4643</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Dato 24</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Esquel</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Tehuelche</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>Motora</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>Pública exclusivamente</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="U26" s="4" t="n">
-        <v>45721</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="27">
@@ -3210,22 +3195,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>López</t>
+          <t>Sosa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Valentina</t>
+          <t>Mateo</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Otro tipo de documentación</t>
+          <t>Documento extranjero</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>90003425</t>
+          <t>90003510</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3235,25 +3220,25 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>90003425</t>
+          <t>90003438</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Perú</t>
         </is>
       </c>
       <c r="J27" s="4" t="n">
-        <v>41583</v>
+        <v>41843</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Belgrano 2262</t>
+          <t>Sarmiento 1366</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3268,37 +3253,37 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Rada Tilly</t>
+          <t>Río Mayo</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>No presenta discapacidad</t>
+          <t>Auditiva</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Vencido</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Otra cobertura</t>
+          <t>Pública exclusivamente</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U27" s="4" t="n">
-        <v>46242</v>
+        <v>45951</v>
       </c>
     </row>
     <row r="28">
@@ -3307,22 +3292,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Gómez</t>
+          <t>Ojeda</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Thiago</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Documento extranjero</t>
+          <t>Sin documentación</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>90003562</t>
+          <t>90003647</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3332,25 +3317,25 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>90003562</t>
+          <t>90003593</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="J28" s="4" t="n">
-        <v>40840</v>
+        <v>40621</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Alberdi 3719</t>
+          <t>Mitre 417</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3365,41 +3350,37 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Rada Tilly</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Mapuche</t>
-        </is>
-      </c>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Visual</t>
+          <t>Mental</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Vencido</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Obra Social</t>
+          <t>Prepaga</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U28" s="4" t="n">
-        <v>46251</v>
+        <v>46058</v>
       </c>
     </row>
     <row r="29">
@@ -3408,12 +3389,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Paz</t>
+          <t>Martínez</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Thiago</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3423,7 +3404,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>90003699</t>
+          <t>90003750</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3433,7 +3414,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>90003699</t>
+          <t>90003741</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3443,15 +3424,15 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="J29" s="4" t="n">
-        <v>40350</v>
+        <v>41322</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Rivadavia 3087</t>
+          <t>Rivadavia 4273</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3466,37 +3447,41 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Río Mayo</t>
+          <t>Gaiman</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 27</t>
+        </is>
+      </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Mental</t>
+          <t>Visceral</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Pública exclusivamente</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>Obra Social</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="U29" s="4" t="n">
-        <v>46182</v>
+        <v>46109</v>
       </c>
     </row>
     <row r="30">
@@ -3505,22 +3490,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sosa</t>
+          <t>Ledesma</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Isabella</t>
+          <t>Valentina</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sin documentación</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>90003836</t>
+          <t>90003849</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3530,25 +3515,25 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>90003836</t>
+          <t>90003912</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="J30" s="4" t="n">
-        <v>41148</v>
+        <v>41463</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Güemes 1431</t>
+          <t>Mitre 4289</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3563,37 +3548,41 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>El Hoyo</t>
+          <t>Trelew</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr"/>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 28</t>
+        </is>
+      </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>No presenta discapacidad</t>
+          <t>Mental</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>En trámite</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Prepaga</t>
+          <t>Pública exclusivamente</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U30" s="4" t="n">
-        <v>45602</v>
+        <v>45845</v>
       </c>
     </row>
     <row r="31">
@@ -3602,12 +3591,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Paz</t>
+          <t>Gómez</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bautista</t>
+          <t>Martina</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3617,7 +3606,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>90003973</t>
+          <t>90004019</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3627,25 +3616,25 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>90003973</t>
+          <t>90004028</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="J31" s="4" t="n">
-        <v>40621</v>
+        <v>41531</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Mitre 417</t>
+          <t>Sarmiento 2671</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3660,23 +3649,27 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>El Maitén</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 29</t>
+        </is>
+      </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Mental</t>
+          <t>Motora</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Vencido</t>
+          <t>No aplica</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3686,11 +3679,11 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U31" s="4" t="n">
-        <v>46054</v>
+        <v>45873</v>
       </c>
     </row>
     <row r="32">
@@ -3699,22 +3692,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Martínez</t>
+          <t>Sosa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Documento extranjero</t>
+          <t>Otro tipo de documentación</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>90004110</t>
+          <t>90004180</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3724,25 +3717,25 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>90004110</t>
+          <t>90004126</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="J32" s="4" t="n">
-        <v>41320</v>
+        <v>41731</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Güemes 668</t>
+          <t>Alberdi 1525</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3757,37 +3750,41 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>El Hoyo</t>
+          <t>Trevelin</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Mapuche-Tehuelche</t>
+        </is>
+      </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>No presenta discapacidad</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>En trámite</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Prepaga</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U32" s="4" t="n">
-        <v>46259</v>
+        <v>45851</v>
       </c>
     </row>
     <row r="33">
@@ -4643,28 +4640,28 @@
   </sheetData>
   <dataValidations count="8">
     <dataValidation sqref="D3:D202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Tipo de documento de identidad&quot;." type="list">
-      <formula1>LISTAS!$J$2:$J$5</formula1>
+      <formula1>Listas!$J$2:$J$5</formula1>
     </dataValidation>
     <dataValidation sqref="H3:H202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Género&quot;." type="list">
-      <formula1>LISTAS!$C$2:$C$4</formula1>
+      <formula1>Listas!$C$2:$C$4</formula1>
     </dataValidation>
     <dataValidation sqref="I3:I202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;País de nacimiento&quot;." type="list">
-      <formula1>LISTAS!$G$2:$G$12</formula1>
+      <formula1>Listas!$G$2:$G$12</formula1>
     </dataValidation>
     <dataValidation sqref="O3:O202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Pertenece a pueblo originario? (o se identifica con algún pueblo originario?)&quot;." type="list">
-      <formula1>LISTAS!$I$2:$I$4</formula1>
+      <formula1>Listas!$I$2:$I$4</formula1>
     </dataValidation>
     <dataValidation sqref="Q3:Q202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Presenta algún tipo de discapacidad?&quot;." type="list">
-      <formula1>LISTAS!$B$2:$B$9</formula1>
+      <formula1>Listas!$B$2:$B$9</formula1>
     </dataValidation>
     <dataValidation sqref="R3:R202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Posee CUD?&quot;." type="list">
-      <formula1>LISTAS!$H$2:$H$7</formula1>
+      <formula1>Listas!$H$2:$H$7</formula1>
     </dataValidation>
     <dataValidation sqref="S3:S202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cobertura salud&quot;." type="list">
-      <formula1>LISTAS!$A$2:$A$6</formula1>
+      <formula1>Listas!$A$2:$A$6</formula1>
     </dataValidation>
     <dataValidation sqref="T3:T202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Tiene hijos/as?&quot;." type="list">
-      <formula1>LISTAS!$I$2:$I$4</formula1>
+      <formula1>Listas!$I$2:$I$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4678,7 +4675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4703,516 +4700,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Dato 1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Trelew</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Dato 2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Río Mayo</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Dato 3</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Esquel</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Dato 4</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Comodoro Rivadavia</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Dato 5</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Trevelin</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Dato 6</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Esquel</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Dato 7</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Rawson</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Dato 8</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Trelew</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Dato 9</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Trevelin</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Dato 10</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Gaiman</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Dato 11</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Sarmiento</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Dato 12</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Lago Puelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Dato 13</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>El Hoyo</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Dato 14</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Sarmiento</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Dato 15</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Gaiman</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Dato 16</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Trevelin</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Dato 17</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Rada Tilly</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Dato 18</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Trelew</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Dato 19</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Gaiman</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Dato 20</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Río Mayo</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Dato 21</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Trevelin</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Dato 22</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Puerto Madryn</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Dato 23</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Esquel</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Dato 24</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Rawson</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Dato 25</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Lago Puelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Dato 26</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Gaiman</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Dato 27</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Rawson</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Dato 28</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Rada Tilly</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Dato 29</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Río Mayo</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Dato 30</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>El Hoyo</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -5220,320 +4707,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Campo</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Indicación para el llenado</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Hoja: NyA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ID del Niño, niña o Adolescente</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Identificador que le asigna el sistema provincial al niño, niña o adolescente. Es la clave con la que las nóminas (MPE, MPI, MPJ) se enganchan a este legajo.
-Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Apellido/s</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Nombre/s</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Tipo de documento de identidad</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Tipo de documento de identidad".</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Nº DNI</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Nº de CUIL</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Otro núero de documentación de identidad (si no cuenta con DNI)</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Género</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Género".</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>País de nacimiento</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "País de nacimiento (legajo)".</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fecha de nacimiento</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.
-Formato de fecha: dd/mm/aaaa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Domicilio actual</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Provincia</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Provincia (nomenclador oficial)".</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Departamento (nomenclador oficial)".</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Localidad</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Localidad (lista de la jurisdicción)".</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>¿Pertenece a pueblo originario? (o se identifica con algún pueblo originario?)</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Pueblo originario (especificar)</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>¿Presenta algún tipo de discapacidad?</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Discapacidad (legajo)".</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>¿Posee CUD?</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Posee CUD?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Cobertura salud</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cobertura salud (legajo)".</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>¿Tiene hijos/as?</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Fecha de actualización</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Formato de fecha: dd/mm/aaaa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Hoja: Prov_Dto_Localidad</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>DEPTO</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>LOCALIDAD</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
